--- a/Tableau_de_synthese_Isaac_Izekor.xlsx
+++ b/Tableau_de_synthese_Isaac_Izekor.xlsx
@@ -988,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ37"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
   <cols>
     <col width="70.42578125" customWidth="1" style="1" min="1" max="1"/>
@@ -1067,7 +1067,7 @@
     <row r="5" ht="40.15" customHeight="1">
       <c r="A5" s="37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adresse URL du portfolio : </t>
+          <t>Adresse URL du portfolio : https://isaac-izekor.github.io/portfolio/</t>
         </is>
       </c>
       <c r="B5" s="38" t="n"/>
@@ -1556,64 +1556,19 @@
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
